--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mylevelshift-my.sharepoint.com/personal/indiranivas_s_levelshift_com/Documents/Documents/work_with_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mylevelshift-my.sharepoint.com/personal/indiranivas_s_levelshift_com/Documents/Documents/L&amp;D  dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_90A6FCDF64F1EBC45049BBB7795DF66D5021C418" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A58E53-7EA8-4BD0-9BCF-4880832FC238}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_90A6FCDF64F1EBC45049BBB7795DF66D5021C418" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9BF93AB-7BD3-464E-8742-0CD31669ADE4}"/>
   <bookViews>
     <workbookView xWindow="-100" yWindow="-100" windowWidth="21467" windowHeight="11443" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -509,8 +509,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="[$-409]mmmm\-yy;@"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -634,21 +634,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -958,6 +958,7 @@
   <dimension ref="A1:T1432"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="10" max="10" width="20.59765625" customWidth="1"/>
     <col min="13" max="13" width="18.69921875" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="27.8984375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="40.09765625" customWidth="1"/>
